--- a/output/pdf_financials_xlsx/APP.xlsx
+++ b/output/pdf_financials_xlsx/APP.xlsx
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.019148</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.039815</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.368888</v>
       </c>
     </row>
     <row r="93">
@@ -3171,7 +3171,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3718,7 +3722,11 @@
           <t>Share-based payment reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" s="5" t="n">
         <v>4.019148</v>
       </c>

--- a/output/pdf_financials_xlsx/APP.xlsx
+++ b/output/pdf_financials_xlsx/APP.xlsx
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1.318518</v>
+        <v>2.214518</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.949334</v>
+        <v>1.586052</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.270939</v>
+        <v>1.545741</v>
       </c>
     </row>
     <row r="11">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.048929</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.013252</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001835</v>
       </c>
     </row>
     <row r="35">
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.048929</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.013252</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001835</v>
       </c>
     </row>
     <row r="37">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.144628</v>
+        <v>0.09569900000000001</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.014843</v>
+        <v>0.001591</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.001835</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5775,17 +5775,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>-2.214518</v>
+        <v>2.214518</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>-1.586052</v>
+        <v>1.586052</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>-1.545741</v>
+        <v>1.545741</v>
       </c>
     </row>
     <row r="101">

--- a/output/pdf_financials_xlsx/APP.xlsx
+++ b/output/pdf_financials_xlsx/APP.xlsx
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.080841</v>
+        <v>0.080307</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0.000696</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.089375</v>
+        <v>-2.089909</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.491016</v>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.080307</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
